--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260807.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260807.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>14.30%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>12.40%</t>
+          <t>12.54%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>10.86%</t>
+          <t>10.94%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>10.08%</t>
+          <t>9.87%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>7.68%</t>
+          <t>7.76%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>35,340,000</t>
+          <t>35,660,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.39%</t>
+          <t>5.38%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>799,890,000</t>
+          <t>804,090,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.56%</t>
+          <t>4.58%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>3.79%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.68%</t>
         </is>
       </c>
     </row>
@@ -814,73 +814,73 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.13%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台指期</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>1,268</t>
+          <t>247,714,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>247,714,000</t>
+          <t>112,800,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>台指期</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>112,270,000</t>
+          <t>1,036</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1019,83 +1019,83 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>36,460,000</t>
+          <t>119,300,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>119,300,000</t>
+          <t>36,460,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>80,890,000</t>
+          <t>117,699,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>117,699,000</t>
+          <t>81,480,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,66 +1107,66 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>76,770,000</t>
+          <t>12,468,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.65%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>8,504,000</t>
+          <t>76,770,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>12,468,000</t>
+          <t>8,504,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -1210,24 +1210,24 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>36,740,000</t>
+          <t>38,623,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,66 +1239,66 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>29,940,000</t>
+          <t>36,740,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>27,842,899</t>
+          <t>29,940,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>38,623,000</t>
+          <t>27,842,899</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>15,470,000</t>
+          <t>13,510,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1364,46 +1364,46 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>13,510,000</t>
+          <t>7,990,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>27,850,000</t>
+          <t>15,470,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>7,990,000</t>
+          <t>27,850,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>長榮鋼</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>29,006,000</t>
+          <t>20,540,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>202609TX</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>長榮鋼</t>
+          <t>台指期</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>20,540,000</t>
+          <t>200</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,35 +1503,39 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>807,789,433</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr"/>
+          <t>29,006,000</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,691,203,893</t>
+          <t>4,812,189,311</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
@@ -1539,17 +1543,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>PFUR_NTD</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>PAYABLES FOR UNITS REDEEMED</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>-224,413,485</t>
+          <t>1,702,069,195</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr"/>
@@ -1557,20 +1561,38 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
+          <t>PFUR_NTD</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>PAYABLES FOR UNITS REDEEMED</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>-224,413,485</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
           <t>RDI_NTD</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>-258,457,514</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr"/>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>-944,671,225</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
